--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -982,77 +982,89 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie o bloco 5 e peça à IA para explicar ao sócio por que a modalidade recomendada é a melhor, ou para listar perguntas que faltam antes de fechar o valor. A decisão continua sua.</t>
+          <t>Copie o bloco 5 e use o prompt "Honorários 07 · Fixo, hora, êxito ou misto: perguntas antes de escolher" da biblioteca do kit para listar o que falta perguntar antes de fechar o valor. A decisão continua sua.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Números em texto</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>As frases da comparação ("Hora mínima sem prejuízo: R$ ...") usam a função FIXED: o separador de milhar e de decimal segue o idioma do Excel (no Excel em português: 1.234,56).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1087,9 +1099,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Simulador de honorários · "&amp;Config!$B$5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Simulador de honorários · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -1132,36 +1144,36 @@
       <c r="J4" s="12" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13">
+      <c r="A5" s="13" t="str">
         <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
-        <v/>
+        <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
         <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"",INDEX($E$52:$E$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
-        <v/>
+        <v>4825.0158</v>
       </c>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="15">
+      <c r="E5" s="15" t="str">
         <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"",INDEX($I$52:$I$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
-        <v/>
+        <v>Baixo</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="16">
         <f>$D$40</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="17">
         <f>$B$15</f>
-        <v/>
+        <v>106.566774193548</v>
       </c>
       <c r="J5" s="12" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="18">
+      <c r="A6" s="18" t="str">
         <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir.")</f>
-        <v/>
+        <v>Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: Êxito. Compare também a coluna 'Se o caso for perdido' antes de decidir.</v>
       </c>
     </row>
     <row r="7">
@@ -1214,11 +1226,11 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>66.06999999999999</v>
+        <v>66.0714</v>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório").</t>
+          <t>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório"). No exemplo, R$ 66,0714 (18.500 ÷ 280 h): a hora mínima abaixo fica igual à da 05 (R$ 106,57).</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1272,7 @@
       </c>
       <c r="B14" s="26">
         <f>B12*B13</f>
-        <v/>
+        <v>33000</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
@@ -1276,7 +1288,7 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(B11/(1-Config!$B$7-Config!$B$8),"")</f>
-        <v/>
+        <v>106.566774193548</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
@@ -1319,7 +1331,7 @@
       </c>
       <c r="C19" s="27">
         <f>IF(B19="","",B19*$B$11)</f>
-        <v/>
+        <v>264.2856</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1345,7 @@
       </c>
       <c r="C20" s="27">
         <f>IF(B20="","",B20*$B$11)</f>
-        <v/>
+        <v>396.4284</v>
       </c>
     </row>
     <row r="21">
@@ -1347,7 +1359,7 @@
       </c>
       <c r="C21" s="27">
         <f>IF(B21="","",B21*$B$11)</f>
-        <v/>
+        <v>792.8568</v>
       </c>
     </row>
     <row r="22">
@@ -1361,7 +1373,7 @@
       </c>
       <c r="C22" s="27">
         <f>IF(B22="","",B22*$B$11)</f>
-        <v/>
+        <v>1321.428</v>
       </c>
     </row>
     <row r="23">
@@ -1375,7 +1387,7 @@
       </c>
       <c r="C23" s="27">
         <f>IF(B23="","",B23*$B$11)</f>
-        <v/>
+        <v>528.5712</v>
       </c>
     </row>
     <row r="24">
@@ -1389,7 +1401,7 @@
       </c>
       <c r="C24" s="27">
         <f>IF(B24="","",B24*$B$11)</f>
-        <v/>
+        <v>198.2142</v>
       </c>
     </row>
     <row r="25">
@@ -1432,11 +1444,11 @@
       </c>
       <c r="B29" s="31">
         <f>SUM(B19:B28)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="C29" s="32">
         <f>SUM(C19:C28)</f>
-        <v/>
+        <v>3501.7842</v>
       </c>
     </row>
     <row r="31">
@@ -1484,7 +1496,7 @@
       </c>
       <c r="D33" s="27">
         <f>IF(B33="","",IF(C33="Sim",0,B33))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1503,7 +1515,7 @@
       </c>
       <c r="D34" s="27">
         <f>IF(B34="","",IF(C34="Sim",0,B34))</f>
-        <v/>
+        <v>300</v>
       </c>
     </row>
     <row r="35">
@@ -1522,7 +1534,7 @@
       </c>
       <c r="D35" s="27">
         <f>IF(B35="","",IF(C35="Sim",0,B35))</f>
-        <v/>
+        <v>150</v>
       </c>
     </row>
     <row r="36">
@@ -1541,7 +1553,7 @@
       </c>
       <c r="D36" s="27">
         <f>IF(B36="","",IF(C36="Sim",0,B36))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1570,11 +1582,11 @@
       </c>
       <c r="B39" s="27">
         <f>SUM(B33:B38)</f>
-        <v/>
+        <v>1250</v>
       </c>
       <c r="D39" s="32">
         <f>SUM(D33:D38)</f>
-        <v/>
+        <v>450</v>
       </c>
     </row>
     <row r="40">
@@ -1585,7 +1597,7 @@
       </c>
       <c r="D40" s="32">
         <f>$C$29+$D$39</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
     </row>
     <row r="42">
@@ -1639,7 +1651,7 @@
         </is>
       </c>
       <c r="B45" s="22" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C45" s="35" t="inlineStr">
         <is>
@@ -1780,43 +1792,43 @@
       </c>
       <c r="B52" s="27">
         <f>$B$44</f>
-        <v/>
+        <v>7000</v>
       </c>
       <c r="C52" s="27">
         <f>B52*Config!$B$7</f>
-        <v/>
+        <v>560</v>
       </c>
       <c r="D52" s="27">
         <f>$D$40</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
       <c r="E52" s="27">
         <f>B52-C52-D52</f>
-        <v/>
+        <v>2488.2158</v>
       </c>
       <c r="F52" s="38">
         <f>IF(B52=0,"",E52/B52)</f>
-        <v/>
+        <v>0.3554594</v>
       </c>
       <c r="G52" s="27">
         <f>E52</f>
-        <v/>
-      </c>
-      <c r="H52" s="39">
+        <v>2488.2158</v>
+      </c>
+      <c r="H52" s="39" t="str">
         <f>IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores")</f>
-        <v/>
-      </c>
-      <c r="I52" s="40">
+        <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
+      </c>
+      <c r="I52" s="40" t="str">
         <f>IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto")</f>
-        <v/>
+        <v>Baixo</v>
       </c>
       <c r="J52" s="41">
         <f>IF(OR(I52="Alto",AND(I52="Médio",Config!$B$12="Não")),-1E+9,E52)</f>
-        <v/>
-      </c>
-      <c r="K52" s="42">
+        <v>2488.2158</v>
+      </c>
+      <c r="K52" s="42" t="str">
         <f>IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)","")</f>
-        <v/>
+        <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
@@ -1827,43 +1839,43 @@
       </c>
       <c r="B53" s="27">
         <f>$B$45*$B$29</f>
-        <v/>
+        <v>9540</v>
       </c>
       <c r="C53" s="27">
         <f>B53*Config!$B$7</f>
-        <v/>
+        <v>763.2</v>
       </c>
       <c r="D53" s="27">
         <f>$D$40</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
       <c r="E53" s="27">
         <f>B53-C53-D53</f>
-        <v/>
+        <v>4825.0158</v>
       </c>
       <c r="F53" s="38">
         <f>IF(B53=0,"",E53/B53)</f>
-        <v/>
+        <v>0.505766855345912</v>
       </c>
       <c r="G53" s="27">
         <f>E53</f>
-        <v/>
-      </c>
-      <c r="H53" s="39">
-        <f>IFERROR("Hora mínima sem prejuízo: R$ "&amp;ROUND($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;$B$45&amp;")","Preencha horas e valores")</f>
-        <v/>
-      </c>
-      <c r="I53" s="40">
+        <v>4825.0158</v>
+      </c>
+      <c r="H53" s="39" t="str">
+        <f>IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores")</f>
+        <v>Hora mínima sem prejuízo: R$ 81.05 (você cobra R$ 180.00)</v>
+      </c>
+      <c r="I53" s="40" t="str">
         <f>IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto")</f>
-        <v/>
+        <v>Baixo</v>
       </c>
       <c r="J53" s="41">
         <f>IF(OR(I53="Alto",AND(I53="Médio",Config!$B$12="Não")),-1E+9,E53)</f>
-        <v/>
-      </c>
-      <c r="K53" s="42">
-        <f>IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;ROUND($B$15,2)&amp;")"),"")</f>
-        <v/>
+        <v>4825.0158</v>
+      </c>
+      <c r="K53" s="42" t="str">
+        <f>IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),"")</f>
+        <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
@@ -1874,43 +1886,43 @@
       </c>
       <c r="B54" s="27">
         <f>$B$46*$B$14</f>
-        <v/>
+        <v>8250</v>
       </c>
       <c r="C54" s="27">
         <f>B54*Config!$B$7</f>
-        <v/>
+        <v>660</v>
       </c>
       <c r="D54" s="27">
         <f>$D$40</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
       <c r="E54" s="27">
         <f>B54-C54-D54</f>
-        <v/>
+        <v>3638.2158</v>
       </c>
       <c r="F54" s="38">
         <f>IF(B54=0,"",E54/B54)</f>
-        <v/>
+        <v>0.440995854545455</v>
       </c>
       <c r="G54" s="27">
         <f>-$D$40</f>
-        <v/>
-      </c>
-      <c r="H54" s="39">
+        <v>-3951.7842</v>
+      </c>
+      <c r="H54" s="39" t="str">
         <f>IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores")</f>
-        <v/>
-      </c>
-      <c r="I54" s="40">
+        <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
+      </c>
+      <c r="I54" s="40" t="str">
         <f>IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto")</f>
-        <v/>
+        <v>Alto</v>
       </c>
       <c r="J54" s="41">
         <f>IF(OR(I54="Alto",AND(I54="Médio",Config!$B$12="Não")),-1E+9,E54)</f>
-        <v/>
-      </c>
-      <c r="K54" s="42">
+        <v>-1000000000</v>
+      </c>
+      <c r="K54" s="42" t="str">
         <f>IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),"")</f>
-        <v/>
+        <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
@@ -1921,43 +1933,43 @@
       </c>
       <c r="B55" s="27">
         <f>$B$47+$B$48*$B$14</f>
-        <v/>
+        <v>9450</v>
       </c>
       <c r="C55" s="27">
         <f>B55*Config!$B$7</f>
-        <v/>
+        <v>756</v>
       </c>
       <c r="D55" s="27">
         <f>$D$40</f>
-        <v/>
+        <v>3951.7842</v>
       </c>
       <c r="E55" s="27">
         <f>B55-C55-D55</f>
-        <v/>
+        <v>4742.2158</v>
       </c>
       <c r="F55" s="38">
         <f>IF(B55=0,"",E55/B55)</f>
-        <v/>
+        <v>0.501821777777778</v>
       </c>
       <c r="G55" s="27">
         <f>$B$47*(1-Config!$B$7)-$D$40</f>
-        <v/>
-      </c>
-      <c r="H55" s="39">
+        <v>188.2158</v>
+      </c>
+      <c r="H55" s="39" t="str">
         <f>IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")</f>
-        <v/>
-      </c>
-      <c r="I55" s="40">
+        <v>A entrada já cobre o custo do caso; o êxito é margem</v>
+      </c>
+      <c r="I55" s="40" t="str">
         <f>IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto")</f>
-        <v/>
+        <v>Baixo</v>
       </c>
       <c r="J55" s="41">
         <f>IF(OR(I55="Alto",AND(I55="Médio",Config!$B$12="Não")),-1E+9,E55)</f>
-        <v/>
-      </c>
-      <c r="K55" s="42">
+        <v>4742.2158</v>
+      </c>
+      <c r="K55" s="42" t="str">
         <f>IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),"")</f>
-        <v/>
+        <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
     <row r="56">
@@ -2114,7 +2126,7 @@
       </c>
       <c r="B6" s="44">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -248,16 +249,16 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="166" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -268,37 +269,37 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -318,14 +319,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -881,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1054,17 +1055,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1166,7 +1179,7 @@
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="17">
         <f>$B$15</f>
-        <v>106.566774193548</v>
+        <v>120.261235544735</v>
       </c>
       <c r="J5" s="12" t="n"/>
     </row>
@@ -1287,12 +1300,12 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>IFERROR(B11/(1-Config!$B$7-Config!$B$8),"")</f>
-        <v>106.566774193548</v>
+        <f>IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")</f>
+        <v>120.261235544735</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>Custo-hora ÷ (1 − impostos − margem).</t>
+          <t>(custo das horas + despesas absorvidas) ÷ horas estimadas ÷ (1 − impostos − margem). Sem caso montado, cai no custo-hora do escritório.</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1876,7 @@
       </c>
       <c r="H53" s="39" t="str">
         <f>IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores")</f>
-        <v>Hora mínima sem prejuízo: R$ 81.05 (você cobra R$ 180.00)</v>
+        <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="40" t="str">
         <f>IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto")</f>
@@ -2124,9 +2137,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="44">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="44" t="n">
+        <v>46279</v>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
+        <f>IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -1241,10 +1241,9 @@
       <c r="B11" s="22" t="n">
         <v>66.0714</v>
       </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório"). No exemplo, R$ 66,0714 (18.500 ÷ 280 h): a hora mínima abaixo fica igual à da 05 (R$ 106,57).</t>
-        </is>
+      <c r="C11" s="23" t="str">
+        <f>"Copie da planilha 05 · Custo-hora (Painel, ""Custo-hora do escritório""). No exemplo, R$ "&amp;FIXED(B11,4)&amp;" (18.500 ÷ 280 h). A hora mínima do caso (abaixo) é MAIOR do que a hora mínima do escritório na 05 sempre que o caso tiver despesa que o escritório absorve: a da 05 cobre só a estrutura, a daqui cobre também essas despesas rateadas pelas horas do caso."</f>
+        <v>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório"). No exemplo, R$ 66,0714 (18.500 ÷ 280 h). A hora mínima do caso (abaixo) é MAIOR do que a hora mínima do escritório na 05 sempre que o caso tiver despesa que o escritório absorve: a da 05 cobre só a estrutura, a daqui cobre também essas despesas rateadas pelas horas do caso.</v>
       </c>
     </row>
     <row r="12">
@@ -1668,7 +1667,7 @@
       </c>
       <c r="C45" s="35" t="inlineStr">
         <is>
-          <t>Cobra as horas trabalhadas. Risco baixo para o escritório; o cliente pode questionar as horas.</t>
+          <t>Cobra as horas trabalhadas: o escritório não absorve hora a mais, mas o cliente pode questionar as horas. Se a hora cobre a hora mínima do caso ou não, quem diz é a coluna Risco ao lado.</t>
         </is>
       </c>
       <c r="D45" s="36" t="n"/>
@@ -1832,15 +1831,15 @@
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="40" t="str">
-        <f>IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto")</f>
+        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
-        <f>IF(OR(I52="Alto",AND(I52="Médio",Config!$B$12="Não")),-1E+9,E52)</f>
+        <f>IF(OR(I52="Alto",I52="Faltam as horas estimadas",AND(I52="Médio",Config!$B$12="Não")),-1E+9,E52)</f>
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)","")</f>
+        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1879,15 +1878,15 @@
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="40" t="str">
-        <f>IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto")</f>
+        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
-        <f>IF(OR(I53="Alto",AND(I53="Médio",Config!$B$12="Não")),-1E+9,E53)</f>
+        <f>IF(OR(I53="Alto",I53="Faltam as horas estimadas",AND(I53="Médio",Config!$B$12="Não")),-1E+9,E53)</f>
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),"")</f>
+        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1926,15 +1925,15 @@
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="40" t="str">
-        <f>IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto")</f>
+        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
-        <f>IF(OR(I54="Alto",AND(I54="Médio",Config!$B$12="Não")),-1E+9,E54)</f>
+        <f>IF(OR(I54="Alto",I54="Faltam as horas estimadas",AND(I54="Médio",Config!$B$12="Não")),-1E+9,E54)</f>
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),"")</f>
+        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1973,15 +1972,15 @@
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="40" t="str">
-        <f>IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto")</f>
+        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
-        <f>IF(OR(I55="Alto",AND(I55="Médio",Config!$B$12="Não")),-1E+9,E55)</f>
+        <f>IF(OR(I55="Alto",I55="Faltam as horas estimadas",AND(I55="Médio",Config!$B$12="Não")),-1E+9,E55)</f>
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),"")</f>
+        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1158,7 +1158,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")))</f>
         <v>120.261235544735</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1342,7 +1342,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="27">
-        <f>IF(B19="","",B19*$B$11)</f>
+        <f>IF(B19="","",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora"))</f>
         <v>264.2856</v>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="27">
-        <f>IF(B20="","",B20*$B$11)</f>
+        <f>IF(B20="","",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora"))</f>
         <v>396.4284</v>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="27">
-        <f>IF(B21="","",B21*$B$11)</f>
+        <f>IF(B21="","",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora"))</f>
         <v>792.8568</v>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="27">
-        <f>IF(B22="","",B22*$B$11)</f>
+        <f>IF(B22="","",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora"))</f>
         <v>1321.428</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="27">
-        <f>IF(B23="","",B23*$B$11)</f>
+        <f>IF(B23="","",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora"))</f>
         <v>528.5712</v>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="27">
-        <f>IF(B24="","",B24*$B$11)</f>
+        <f>IF(B24="","",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora"))</f>
         <v>198.2142</v>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       <c r="A25" s="21" t="n"/>
       <c r="B25" s="29" t="n"/>
       <c r="C25" s="27">
-        <f>IF(B25="","",B25*$B$11)</f>
+        <f>IF(B25="","",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora"))</f>
         <v/>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       <c r="A26" s="21" t="n"/>
       <c r="B26" s="29" t="n"/>
       <c r="C26" s="27">
-        <f>IF(B26="","",B26*$B$11)</f>
+        <f>IF(B26="","",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora"))</f>
         <v/>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       <c r="A27" s="21" t="n"/>
       <c r="B27" s="29" t="n"/>
       <c r="C27" s="27">
-        <f>IF(B27="","",B27*$B$11)</f>
+        <f>IF(B27="","",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora"))</f>
         <v/>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       <c r="A28" s="21" t="n"/>
       <c r="B28" s="29" t="n"/>
       <c r="C28" s="27">
-        <f>IF(B28="","",B28*$B$11)</f>
+        <f>IF(B28="","",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora"))</f>
         <v/>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="D40" s="32">
-        <f>$C$29+$D$39</f>
+        <f>IF(ISNUMBER($B$11),$C$29+$D$39,"Falta o custo-hora (B11)")</f>
         <v>3951.7842</v>
       </c>
     </row>
@@ -1815,31 +1815,31 @@
         <v>3951.7842</v>
       </c>
       <c r="E52" s="27">
-        <f>B52-C52-D52</f>
+        <f>IF(ISNUMBER(D52),B52-C52-D52,"")</f>
         <v>2488.2158</v>
       </c>
       <c r="F52" s="38">
-        <f>IF(B52=0,"",E52/B52)</f>
+        <f>IF(OR(B52=0,NOT(ISNUMBER(E52))),"",E52/B52)</f>
         <v>0.3554594</v>
       </c>
       <c r="G52" s="27">
-        <f>E52</f>
+        <f>IF(ISNUMBER($D$40),E52,"")</f>
         <v>2488.2158</v>
       </c>
       <c r="H52" s="39" t="str">
-        <f>IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores")</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores"))</f>
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="40" t="str">
-        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
-        <f>IF(OR(I52="Alto",I52="Faltam as horas estimadas",AND(I52="Médio",Config!$B$12="Não")),-1E+9,E52)</f>
+        <f>IF(OR(I52="Baixo",AND(I52="Médio",Config!$B$12="Sim")),E52,-1E+9)</f>
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1862,31 +1862,31 @@
         <v>3951.7842</v>
       </c>
       <c r="E53" s="27">
-        <f>B53-C53-D53</f>
+        <f>IF(ISNUMBER(D53),B53-C53-D53,"")</f>
         <v>4825.0158</v>
       </c>
       <c r="F53" s="38">
-        <f>IF(B53=0,"",E53/B53)</f>
+        <f>IF(OR(B53=0,NOT(ISNUMBER(E53))),"",E53/B53)</f>
         <v>0.505766855345912</v>
       </c>
       <c r="G53" s="27">
-        <f>E53</f>
+        <f>IF(ISNUMBER($D$40),E53,"")</f>
         <v>4825.0158</v>
       </c>
       <c r="H53" s="39" t="str">
-        <f>IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores")</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores"))</f>
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="40" t="str">
-        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
-        <f>IF(OR(I53="Alto",I53="Faltam as horas estimadas",AND(I53="Médio",Config!$B$12="Não")),-1E+9,E53)</f>
+        <f>IF(OR(I53="Baixo",AND(I53="Médio",Config!$B$12="Sim")),E53,-1E+9)</f>
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1909,31 +1909,31 @@
         <v>3951.7842</v>
       </c>
       <c r="E54" s="27">
-        <f>B54-C54-D54</f>
+        <f>IF(ISNUMBER(D54),B54-C54-D54,"")</f>
         <v>3638.2158</v>
       </c>
       <c r="F54" s="38">
-        <f>IF(B54=0,"",E54/B54)</f>
+        <f>IF(OR(B54=0,NOT(ISNUMBER(E54))),"",E54/B54)</f>
         <v>0.440995854545455</v>
       </c>
       <c r="G54" s="27">
-        <f>-$D$40</f>
+        <f>IF(ISNUMBER($D$40),-$D$40,"")</f>
         <v>-3951.7842</v>
       </c>
       <c r="H54" s="39" t="str">
-        <f>IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores")</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores"))</f>
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="40" t="str">
-        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
-        <f>IF(OR(I54="Alto",I54="Faltam as horas estimadas",AND(I54="Médio",Config!$B$12="Não")),-1E+9,E54)</f>
+        <f>IF(OR(I54="Baixo",AND(I54="Médio",Config!$B$12="Sim")),E54,-1E+9)</f>
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1956,31 +1956,31 @@
         <v>3951.7842</v>
       </c>
       <c r="E55" s="27">
-        <f>B55-C55-D55</f>
+        <f>IF(ISNUMBER(D55),B55-C55-D55,"")</f>
         <v>4742.2158</v>
       </c>
       <c r="F55" s="38">
-        <f>IF(B55=0,"",E55/B55)</f>
+        <f>IF(OR(B55=0,NOT(ISNUMBER(E55))),"",E55/B55)</f>
         <v>0.501821777777778</v>
       </c>
       <c r="G55" s="27">
-        <f>$B$47*(1-Config!$B$7)-$D$40</f>
+        <f>IF(ISNUMBER($D$40),$B$47*(1-Config!$B$7)-$D$40,"")</f>
         <v>188.2158</v>
       </c>
       <c r="H55" s="39" t="str">
-        <f>IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores"))</f>
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="40" t="str">
-        <f>IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
-        <f>IF(OR(I55="Alto",I55="Faltam as horas estimadas",AND(I55="Médio",Config!$B$12="Não")),-1E+9,E55)</f>
+        <f>IF(OR(I55="Baixo",AND(I55="Médio",Config!$B$12="Sim")),E55,-1E+9)</f>
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
   </mergeCells>
   <conditionalFormatting sqref="I52:I55">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>I52="Alto"</formula>
+      <formula>OR(I52="Alto",I52="Falta o custo-hora",I52="Margens inválidas")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>I52="Médio"</formula>
@@ -2330,7 +2330,25 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="6">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e impostos + margem abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
+      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Percentual entre 0 % e 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Percentual entre 0 % e 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Percentual entre 0 % e 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1158,7 +1158,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="18" t="str">
-        <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir.")</f>
+        <f>IF(OR(COUNT($E$52:$E$55)=0,$B$29&lt;=0),"Sem recomendação ainda: complete o custo-hora, as horas estimadas e a Config.",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir."))</f>
         <v>Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: Êxito. Compare também a coluna 'Se o caso for perdido' antes de decidir.</v>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")))</f>
         <v>120.261235544735</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1459,7 +1459,7 @@
         <v>53</v>
       </c>
       <c r="C29" s="32">
-        <f>SUM(C19:C28)</f>
+        <f>IF(ISNUMBER($B$11),SUM(C19:C28),"falta o custo-hora")</f>
         <v>3501.7842</v>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
         <v>7000</v>
       </c>
       <c r="C52" s="27">
-        <f>B52*Config!$B$7</f>
+        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B52*Config!$B$7)</f>
         <v>560</v>
       </c>
       <c r="D52" s="27">
@@ -1815,7 +1815,7 @@
         <v>3951.7842</v>
       </c>
       <c r="E52" s="27">
-        <f>IF(ISNUMBER(D52),B52-C52-D52,"")</f>
+        <f>IF(AND(ISNUMBER(C52),ISNUMBER(D52)),B52-C52-D52,"")</f>
         <v>2488.2158</v>
       </c>
       <c r="F52" s="38">
@@ -1823,15 +1823,15 @@
         <v>0.3554594</v>
       </c>
       <c r="G52" s="27">
-        <f>IF(ISNUMBER($D$40),E52,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),E52,"")</f>
         <v>2488.2158</v>
       </c>
       <c r="H52" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores")))</f>
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
@@ -1839,7 +1839,7 @@
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
         <v>9540</v>
       </c>
       <c r="C53" s="27">
-        <f>B53*Config!$B$7</f>
+        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B53*Config!$B$7)</f>
         <v>763.2</v>
       </c>
       <c r="D53" s="27">
@@ -1862,7 +1862,7 @@
         <v>3951.7842</v>
       </c>
       <c r="E53" s="27">
-        <f>IF(ISNUMBER(D53),B53-C53-D53,"")</f>
+        <f>IF(AND(ISNUMBER(C53),ISNUMBER(D53)),B53-C53-D53,"")</f>
         <v>4825.0158</v>
       </c>
       <c r="F53" s="38">
@@ -1870,15 +1870,15 @@
         <v>0.505766855345912</v>
       </c>
       <c r="G53" s="27">
-        <f>IF(ISNUMBER($D$40),E53,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),E53,"")</f>
         <v>4825.0158</v>
       </c>
       <c r="H53" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores")))</f>
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
@@ -1886,7 +1886,7 @@
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
         <v>8250</v>
       </c>
       <c r="C54" s="27">
-        <f>B54*Config!$B$7</f>
+        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B54*Config!$B$7)</f>
         <v>660</v>
       </c>
       <c r="D54" s="27">
@@ -1909,7 +1909,7 @@
         <v>3951.7842</v>
       </c>
       <c r="E54" s="27">
-        <f>IF(ISNUMBER(D54),B54-C54-D54,"")</f>
+        <f>IF(AND(ISNUMBER(C54),ISNUMBER(D54)),B54-C54-D54,"")</f>
         <v>3638.2158</v>
       </c>
       <c r="F54" s="38">
@@ -1917,15 +1917,15 @@
         <v>0.440995854545455</v>
       </c>
       <c r="G54" s="27">
-        <f>IF(ISNUMBER($D$40),-$D$40,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),-$D$40,"")</f>
         <v>-3951.7842</v>
       </c>
       <c r="H54" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores")))</f>
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
@@ -1933,7 +1933,7 @@
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         <v>9450</v>
       </c>
       <c r="C55" s="27">
-        <f>B55*Config!$B$7</f>
+        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B55*Config!$B$7)</f>
         <v>756</v>
       </c>
       <c r="D55" s="27">
@@ -1956,7 +1956,7 @@
         <v>3951.7842</v>
       </c>
       <c r="E55" s="27">
-        <f>IF(ISNUMBER(D55),B55-C55-D55,"")</f>
+        <f>IF(AND(ISNUMBER(C55),ISNUMBER(D55)),B55-C55-D55,"")</f>
         <v>4742.2158</v>
       </c>
       <c r="F55" s="38">
@@ -1964,15 +1964,15 @@
         <v>0.501821777777778</v>
       </c>
       <c r="G55" s="27">
-        <f>IF(ISNUMBER($D$40),$B$47*(1-Config!$B$7)-$D$40,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),$B$47*(1-Config!$B$7)-$D$40,"")</f>
         <v>188.2158</v>
       </c>
       <c r="H55" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores"))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")))</f>
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
@@ -1980,7 +1980,7 @@
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF(((1-Config!$B$7-Config!$B$8)&lt;=0),"Impostos + margem em Config somam 100 % ou mais: nenhum preço cobre isso. Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2271,6 +2271,20 @@
       <c r="E12" s="21" t="n"/>
     </row>
     <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Impostos e margem conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="str">
+        <f>IF(AND(ISNUMBER(B7),ISNUMBER(B8)),IF(AND(B7&gt;=0,B7&lt;1,B8&gt;=0,B8&lt;1,B7+B8&lt;1),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>"Não" suspende hora mínima, margens, risco e recomendação no Simulador até a Config ser corrigida.</t>
+        </is>
+      </c>
       <c r="E13" s="21" t="n"/>
     </row>
     <row r="14">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1158,17 +1158,17 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0))))))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(Config!$B$14&lt;&gt;"Sim","Corrija as regras de risco em Config",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
-        <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"",INDEX($E$52:$E$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
+        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($E$52:$E$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
         <v>4825.0158</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15" t="str">
-        <f>IF(MAX($J$52:$J$55)&lt;=-1E+9,"",INDEX($I$52:$I$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
+        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($I$52:$I$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
         <v>Baixo</v>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="18" t="str">
-        <f>IF(OR(COUNT($E$52:$E$55)=0,$B$29&lt;=0),"Sem recomendação ainda: complete o custo-hora, as horas estimadas e a Config.",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir."))</f>
+        <f>IF(OR(COUNT($E$52:$E$55)=0,$B$29&lt;=0,Config!$B$14&lt;&gt;"Sim"),"Sem recomendação ainda: complete o custo-hora, as horas estimadas e a Config (margens e regras de risco).",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir."))</f>
         <v>Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: Êxito. Compare também a coluna 'Se o caso for perdido' antes de decidir.</v>
       </c>
     </row>
@@ -1241,9 +1241,10 @@
       <c r="B11" s="22" t="n">
         <v>66.0714</v>
       </c>
-      <c r="C11" s="23" t="str">
-        <f>"Copie da planilha 05 · Custo-hora (Painel, ""Custo-hora do escritório""). No exemplo, R$ "&amp;FIXED(B11,4)&amp;" (18.500 ÷ 280 h). A hora mínima do caso (abaixo) é MAIOR do que a hora mínima do escritório na 05 sempre que o caso tiver despesa que o escritório absorve: a da 05 cobre só a estrutura, a daqui cobre também essas despesas rateadas pelas horas do caso."</f>
-        <v>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório"). No exemplo, R$ 66,0714 (18.500 ÷ 280 h). A hora mínima do caso (abaixo) é MAIOR do que a hora mínima do escritório na 05 sempre que o caso tiver despesa que o escritório absorve: a da 05 cobre só a estrutura, a daqui cobre também essas despesas rateadas pelas horas do caso.</v>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Copie da planilha 05 · Custo-hora (Painel, "Custo-hora do escritório"). No exemplo, R$ 66,0714 (18.500 ÷ 280 h). A hora mínima do caso (abaixo) é MAIOR do que a hora mínima do escritório na 05 sempre que o caso tiver despesa que o escritório absorve: a da 05 cobre só a estrutura, a daqui cobre também essas despesas rateadas pelas horas do caso.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1827,11 +1828,11 @@
         <v>2488.2158</v>
       </c>
       <c r="H52" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")","Preencha horas e valores")))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Custo-hora zero: o fixo cobre as despesas absorvidas","Custo-hora zero, mas o fixo não cobre as despesas absorvidas"),"Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")"),"Preencha horas e valores")))</f>
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$29=0,"Alto",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1&gt;=Config!$B$11,"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)/$B$11&gt;=$B$29,"Médio","Alto"))),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar")))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
@@ -1839,7 +1840,7 @@
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR("Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)",""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),"")))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1878,7 +1879,7 @@
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar")))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
@@ -1886,7 +1887,7 @@
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),"")))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1921,11 +1922,11 @@
         <v>-3951.7842</v>
       </c>
       <c r="H54" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)","Preencha horas e valores")))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF(($B$46*$B$12*(1-Config!$B$7))&lt;=0,"Sem percentual de êxito ou valor em discussão: o êxito não paga o custo","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")))</f>
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF(OR($B$13&lt;Config!$B$9,$B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10),"Alto","Médio"),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar")))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
@@ -1933,7 +1934,7 @@
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF($B$13&lt;$D$40/($B$46*$B$12*(1-Config!$B$7))+Config!$B$10,"Chance estimada perto demais do ponto de equilíbrio","Só recebe no fim; o caixa precisa aguentar até lá")),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),"")))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1968,11 +1969,11 @@
         <v>188.2158</v>
       </c>
       <c r="H55" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"A entrada já cobre o custo do caso; o êxito é margem","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"A entrada já cobre o custo do caso; o êxito é margem",IF(($B$48*$B$12*(1-Config!$B$7))&lt;=0,"A entrada não cobre o custo e não há êxito que complete","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)")),"Preencha horas e valores")))</f>
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IFERROR(IF($B$13&lt;MAX(0,($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7)))+Config!$B$10,"Alto",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Médio","Baixo")),"Alto"))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar")))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
@@ -1980,7 +1981,7 @@
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IFERROR(IF($B$47*(1-Config!$B$7)&gt;=$D$40,"Entrada cobre o custo: mesmo perdendo, não há prejuízo",IF($B$47*(1-Config!$B$7)&lt;$D$40,"Entrada não cobre todo o custo; parte depende do êxito","")),""))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),"")))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2015,7 +2016,7 @@
   </mergeCells>
   <conditionalFormatting sqref="I52:I55">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(I52="Alto",I52="Falta o custo-hora",I52="Margens inválidas")</formula>
+      <formula>OR(I52="Alto",I52="Falta o custo-hora",I52="Margens inválidas",I52="Regra de risco inválida (Config)",I52="Sem base para classificar")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>I52="Médio"</formula>
@@ -2288,6 +2289,20 @@
       <c r="E13" s="21" t="n"/>
     </row>
     <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>Regras de risco conferem? (calculado)</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="str">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),IF(AND(B9&gt;=0,B9&lt;=1,B10&gt;=0,B10&lt;=1,B11&gt;=0,B11&lt;=1,OR(B12="Sim",B12="Não")),"Sim","Não"),"Não")</f>
+        <v>Sim</v>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>"Não" suspende a recomendação: chance mínima e folgas de 0 % a 100 %, e "Aceitar risco médio" = Sim ou Não.</t>
+        </is>
+      </c>
       <c r="E14" s="21" t="n"/>
     </row>
     <row r="15">
@@ -2346,10 +2361,10 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B7),AND(B7&gt;=0,B7&lt;1,B7+N(B8)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e impostos + margem abaixo de 100 %: senão nenhum preço cobre o custo." type="custom">
-      <formula1>=AND(ISNUMBER(B8),B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B8),AND(B8&gt;=0,B8&lt;1,B8+N(B7)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Percentual entre 0 % e 100 %." type="decimal" operator="between">
       <formula1>0</formula1>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -288,6 +288,9 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -315,9 +318,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1158,17 +1158,17 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(Config!$B$14&lt;&gt;"Sim","Corrija as regras de risco em Config",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))))))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF(NOT(ISNUMBER($D$40)),"Corrija horas ou despesas",IF($B$16&lt;&gt;"Sim","Complete os dados do caso",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(Config!$B$14&lt;&gt;"Sim","Corrija as regras de risco em Config",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))))))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
-        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($E$52:$E$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
+        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",$B$16&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($E$52:$E$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
         <v>4825.0158</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15" t="str">
-        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($I$52:$I$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
+        <f>IF(OR(Config!$B$14&lt;&gt;"Sim",$B$16&lt;&gt;"Sim",MAX($J$52:$J$55)&lt;=-1E+9),"",INDEX($I$52:$I$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))</f>
         <v>Baixo</v>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="18" t="str">
-        <f>IF(OR(COUNT($E$52:$E$55)=0,$B$29&lt;=0,Config!$B$14&lt;&gt;"Sim"),"Sem recomendação ainda: complete o custo-hora, as horas estimadas e a Config (margens e regras de risco).",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir."))</f>
+        <f>IF(OR(COUNT($E$52:$E$55)=0,$B$29&lt;=0,Config!$B$14&lt;&gt;"Sim",$B$16&lt;&gt;"Sim"),"Sem recomendação ainda: complete o custo-hora, as horas, os dados do caso (B16) e a Config (margens e regras de risco).",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma modalidade ficou com risco aceitável. Reveja horas, valores ou a chance de êxito; a maior margem em números seria "&amp;INDEX($A$52:$A$55,MATCH(MAX($E$52:$E$55),$E$52:$E$55,0))&amp;".","Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: "&amp;IF(COUNTIF($I$52:$I$55,"Alto")=0,"nenhuma",LEFT(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""),LEN(IF($I$52="Alto","Fixo, ","")&amp;IF($I$53="Alto","Hora, ","")&amp;IF($I$54="Alto","Êxito, ","")&amp;IF($I$55="Alto","Misto, ",""))-2))&amp;". Compare também a coluna 'Se o caso for perdido' antes de decidir."))</f>
         <v>Regra: maior margem esperada entre as modalidades com risco aceitável. Fora por risco alto: Êxito. Compare também a coluna 'Se o caso for perdido' antes de decidir.</v>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>B12*B13</f>
+        <f>IF(AND(IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE)),B12*B13,"falta valor ou chance")</f>
         <v>33000</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -1300,12 +1300,28 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),"")))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),""))))</f>
         <v>120.261235544735</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
           <t>(custo das horas + despesas absorvidas) ÷ horas estimadas ÷ (1 − impostos − margem). Sem caso montado, cai no custo-hora do escritório.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Dados do caso conferem?</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="str">
+        <f>IF(NOT(IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE)),"falta o valor em discussão (B12)",IF(NOT(IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE)),"falta a chance de êxito, de 0 a 100 % (B13)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"falta o valor do fixo (B44)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"falta a hora cobrada (B45)",IF(NOT(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE)),"falta o % de êxito, de 0 a 100 % (B46)",IF(NOT(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE)),"falta a entrada do misto (B47)",IF(NOT(IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE)),"falta o % do misto, de 0 a 100 % (B48)","Sim")))))))</f>
+        <v>Sim</v>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>"Sim" quando valor em discussão, chance e os valores das quatro modalidades são números no domínio certo. Zero digitado vale; vazio ou texto suspende a modalidade que usa o dado e a recomendação.</t>
         </is>
       </c>
     </row>
@@ -1317,17 +1333,17 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Horas estimadas</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Custo (R$)</t>
         </is>
@@ -1339,11 +1355,11 @@
           <t>Reunião inicial e análise dos documentos</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="27">
-        <f>IF(B19="","",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B19="","",IF(NOT(ISNUMBER(B19)),"horas inválidas",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora")))</f>
         <v>264.2856</v>
       </c>
     </row>
@@ -1353,11 +1369,11 @@
           <t>Estudo do caso e estratégia</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>6</v>
       </c>
       <c r="C20" s="27">
-        <f>IF(B20="","",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B20="","",IF(NOT(ISNUMBER(B20)),"horas inválidas",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora")))</f>
         <v>396.4284</v>
       </c>
     </row>
@@ -1367,11 +1383,11 @@
           <t>Redação e protocolo inicial</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>12</v>
       </c>
       <c r="C21" s="27">
-        <f>IF(B21="","",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B21="","",IF(NOT(ISNUMBER(B21)),"horas inválidas",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora")))</f>
         <v>792.8568</v>
       </c>
     </row>
@@ -1381,11 +1397,11 @@
           <t>Acompanhamento e manifestações</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="27">
-        <f>IF(B22="","",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B22="","",IF(NOT(ISNUMBER(B22)),"horas inválidas",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora")))</f>
         <v>1321.428</v>
       </c>
     </row>
@@ -1395,11 +1411,11 @@
           <t>Audiências e reuniões</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>8</v>
       </c>
       <c r="C23" s="27">
-        <f>IF(B23="","",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B23="","",IF(NOT(ISNUMBER(B23)),"horas inválidas",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora")))</f>
         <v>528.5712</v>
       </c>
     </row>
@@ -1409,58 +1425,58 @@
           <t>Encerramento e prestação de contas</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="27">
-        <f>IF(B24="","",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B24="","",IF(NOT(ISNUMBER(B24)),"horas inválidas",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora")))</f>
         <v>198.2142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n"/>
-      <c r="B25" s="29" t="n"/>
+      <c r="B25" s="30" t="n"/>
       <c r="C25" s="27">
-        <f>IF(B25="","",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B25="","",IF(NOT(ISNUMBER(B25)),"horas inválidas",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="n"/>
-      <c r="B26" s="29" t="n"/>
+      <c r="B26" s="30" t="n"/>
       <c r="C26" s="27">
-        <f>IF(B26="","",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B26="","",IF(NOT(ISNUMBER(B26)),"horas inválidas",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="n"/>
-      <c r="B27" s="29" t="n"/>
+      <c r="B27" s="30" t="n"/>
       <c r="C27" s="27">
-        <f>IF(B27="","",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B27="","",IF(NOT(ISNUMBER(B27)),"horas inválidas",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="n"/>
-      <c r="B28" s="29" t="n"/>
+      <c r="B28" s="30" t="n"/>
       <c r="C28" s="27">
-        <f>IF(B28="","",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora"))</f>
+        <f>IF(B28="","",IF(NOT(ISNUMBER(B28)),"horas inválidas",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Total de horas e custo das horas</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>SUM(B19:B28)</f>
         <v>53</v>
       </c>
-      <c r="C29" s="32">
-        <f>IF(ISNUMBER($B$11),SUM(C19:C28),"falta o custo-hora")</f>
+      <c r="C29" s="33">
+        <f>IF(NOT(ISNUMBER($B$11)),"falta o custo-hora",IF(COUNT(B19:B28)&lt;COUNTA(B19:B28),"horas com texto",SUM(C19:C28)))</f>
         <v>3501.7842</v>
       </c>
     </row>
@@ -1472,22 +1488,22 @@
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>Despesa</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>Valor (R$)</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
         <is>
           <t>Cliente reembolsa?</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="29" t="inlineStr">
         <is>
           <t>Custo para o escritório (R$)</t>
         </is>
@@ -1502,13 +1518,13 @@
       <c r="B33" s="22" t="n">
         <v>800</v>
       </c>
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="D33" s="27">
-        <f>IF(B33="","",IF(C33="Sim",0,B33))</f>
+        <f>IF(B33="","",IF(NOT(ISNUMBER(B33)),"valor inválido",IF(C33="Sim",0,B33)))</f>
         <v>0</v>
       </c>
     </row>
@@ -1521,13 +1537,13 @@
       <c r="B34" s="22" t="n">
         <v>300</v>
       </c>
-      <c r="C34" s="33" t="inlineStr">
+      <c r="C34" s="34" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
       <c r="D34" s="27">
-        <f>IF(B34="","",IF(C34="Sim",0,B34))</f>
+        <f>IF(B34="","",IF(NOT(ISNUMBER(B34)),"valor inválido",IF(C34="Sim",0,B34)))</f>
         <v>300</v>
       </c>
     </row>
@@ -1540,13 +1556,13 @@
       <c r="B35" s="22" t="n">
         <v>150</v>
       </c>
-      <c r="C35" s="33" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
       <c r="D35" s="27">
-        <f>IF(B35="","",IF(C35="Sim",0,B35))</f>
+        <f>IF(B35="","",IF(NOT(ISNUMBER(B35)),"valor inválido",IF(C35="Sim",0,B35)))</f>
         <v>150</v>
       </c>
     </row>
@@ -1559,36 +1575,36 @@
       <c r="B36" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="33" t="inlineStr">
+      <c r="C36" s="34" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
       <c r="D36" s="27">
-        <f>IF(B36="","",IF(C36="Sim",0,B36))</f>
+        <f>IF(B36="","",IF(NOT(ISNUMBER(B36)),"valor inválido",IF(C36="Sim",0,B36)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="21" t="n"/>
       <c r="B37" s="22" t="n"/>
-      <c r="C37" s="33" t="n"/>
+      <c r="C37" s="34" t="n"/>
       <c r="D37" s="27">
-        <f>IF(B37="","",IF(C37="Sim",0,B37))</f>
+        <f>IF(B37="","",IF(NOT(ISNUMBER(B37)),"valor inválido",IF(C37="Sim",0,B37)))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="n"/>
       <c r="B38" s="22" t="n"/>
-      <c r="C38" s="33" t="n"/>
+      <c r="C38" s="34" t="n"/>
       <c r="D38" s="27">
-        <f>IF(B38="","",IF(C38="Sim",0,B38))</f>
+        <f>IF(B38="","",IF(NOT(ISNUMBER(B38)),"valor inválido",IF(C38="Sim",0,B38)))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>Total de despesas · custo para o escritório</t>
         </is>
@@ -1597,19 +1613,19 @@
         <f>SUM(B33:B38)</f>
         <v>1250</v>
       </c>
-      <c r="D39" s="32">
-        <f>SUM(D33:D38)</f>
+      <c r="D39" s="33">
+        <f>IF(COUNT(B33:B38)&lt;COUNTA(B33:B38),"despesa com texto",SUM(D33:D38))</f>
         <v>450</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>Custo total do caso (horas + despesas que o escritório absorve)</t>
         </is>
       </c>
-      <c r="D40" s="32">
-        <f>IF(ISNUMBER($B$11),$C$29+$D$39,"Falta o custo-hora (B11)")</f>
+      <c r="D40" s="33">
+        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($C$29)),"Horas com texto (bloco 2)",IF(NOT(ISNUMBER($D$39)),"Despesa com texto (bloco 3)",$C$29+$D$39)))</f>
         <v>3951.7842</v>
       </c>
     </row>
@@ -1621,24 +1637,24 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Modalidade</t>
         </is>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>Como funciona</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Fixo · valor fechado (R$)</t>
         </is>
@@ -1646,19 +1662,19 @@
       <c r="B44" s="24" t="n">
         <v>7000</v>
       </c>
-      <c r="C44" s="35" t="inlineStr">
+      <c r="C44" s="36" t="inlineStr">
         <is>
           <t>Um valor pelo caso inteiro, independente das horas. Risco: o caso consumir mais horas que o estimado.</t>
         </is>
       </c>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
-      <c r="F44" s="36" t="n"/>
-      <c r="G44" s="36" t="n"/>
-      <c r="H44" s="37" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="37" t="n"/>
+      <c r="G44" s="37" t="n"/>
+      <c r="H44" s="38" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>Hora · valor da hora cobrada (R$)</t>
         </is>
@@ -1666,19 +1682,19 @@
       <c r="B45" s="22" t="n">
         <v>180</v>
       </c>
-      <c r="C45" s="35" t="inlineStr">
+      <c r="C45" s="36" t="inlineStr">
         <is>
           <t>Cobra as horas trabalhadas: o escritório não absorve hora a mais, mas o cliente pode questionar as horas. Se a hora cobre a hora mínima do caso ou não, quem diz é a coluna Risco ao lado.</t>
         </is>
       </c>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
-      <c r="F45" s="36" t="n"/>
-      <c r="G45" s="36" t="n"/>
-      <c r="H45" s="37" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="37" t="n"/>
+      <c r="G45" s="37" t="n"/>
+      <c r="H45" s="38" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>Êxito · % sobre o resultado</t>
         </is>
@@ -1686,19 +1702,19 @@
       <c r="B46" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="C46" s="35" t="inlineStr">
+      <c r="C46" s="36" t="inlineStr">
         <is>
           <t>Só recebe se o caso der certo, no fim. Risco: trabalhar e não receber.</t>
         </is>
       </c>
-      <c r="D46" s="36" t="n"/>
-      <c r="E46" s="36" t="n"/>
-      <c r="F46" s="36" t="n"/>
-      <c r="G46" s="36" t="n"/>
-      <c r="H46" s="37" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="37" t="n"/>
+      <c r="G46" s="37" t="n"/>
+      <c r="H46" s="38" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>Misto · entrada fixa (R$)</t>
         </is>
@@ -1706,19 +1722,19 @@
       <c r="B47" s="24" t="n">
         <v>4500</v>
       </c>
-      <c r="C47" s="35" t="inlineStr">
+      <c r="C47" s="36" t="inlineStr">
         <is>
           <t>Uma parte fixa no início (cobre o custo) mais um percentual sobre o resultado.</t>
         </is>
       </c>
-      <c r="D47" s="36" t="n"/>
-      <c r="E47" s="36" t="n"/>
-      <c r="F47" s="36" t="n"/>
-      <c r="G47" s="36" t="n"/>
-      <c r="H47" s="37" t="n"/>
+      <c r="D47" s="37" t="n"/>
+      <c r="E47" s="37" t="n"/>
+      <c r="F47" s="37" t="n"/>
+      <c r="G47" s="37" t="n"/>
+      <c r="H47" s="38" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>Misto · % sobre o resultado</t>
         </is>
@@ -1726,12 +1742,12 @@
       <c r="B48" s="25" t="n">
         <v>0.15</v>
       </c>
-      <c r="C48" s="35" t="inlineStr"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-      <c r="G48" s="36" t="n"/>
-      <c r="H48" s="37" t="n"/>
+      <c r="C48" s="36" t="inlineStr"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="38" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -1741,74 +1757,74 @@
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>Modalidade</t>
         </is>
       </c>
-      <c r="B51" s="28" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>Receita esperada (R$)</t>
         </is>
       </c>
-      <c r="C51" s="28" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Impostos e taxas (R$)</t>
         </is>
       </c>
-      <c r="D51" s="28" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>Custo do caso (R$)</t>
         </is>
       </c>
-      <c r="E51" s="28" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>Margem esperada (R$)</t>
         </is>
       </c>
-      <c r="F51" s="28" t="inlineStr">
+      <c r="F51" s="29" t="inlineStr">
         <is>
           <t>Margem (%)</t>
         </is>
       </c>
-      <c r="G51" s="28" t="inlineStr">
+      <c r="G51" s="29" t="inlineStr">
         <is>
           <t>Se o caso for perdido (R$)</t>
         </is>
       </c>
-      <c r="H51" s="28" t="inlineStr">
+      <c r="H51" s="29" t="inlineStr">
         <is>
           <t>Ponto de equilíbrio</t>
         </is>
       </c>
-      <c r="I51" s="28" t="inlineStr">
+      <c r="I51" s="29" t="inlineStr">
         <is>
           <t>Risco</t>
         </is>
       </c>
-      <c r="J51" s="28" t="inlineStr">
+      <c r="J51" s="29" t="inlineStr">
         <is>
           <t>Pontuação</t>
         </is>
       </c>
-      <c r="K51" s="28" t="inlineStr">
+      <c r="K51" s="29" t="inlineStr">
         <is>
           <t>Por que este risco</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Fixo</t>
         </is>
       </c>
       <c r="B52" s="27">
-        <f>$B$44</f>
+        <f>IF(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE),$B$44,"")</f>
         <v>7000</v>
       </c>
       <c r="C52" s="27">
-        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B52*Config!$B$7)</f>
+        <f>IF(OR((Config!$B$13&lt;&gt;"Sim"),NOT(ISNUMBER(B52))),"",B52*Config!$B$7)</f>
         <v>560</v>
       </c>
       <c r="D52" s="27">
@@ -1819,20 +1835,20 @@
         <f>IF(AND(ISNUMBER(C52),ISNUMBER(D52)),B52-C52-D52,"")</f>
         <v>2488.2158</v>
       </c>
-      <c r="F52" s="38">
+      <c r="F52" s="39">
         <f>IF(OR(B52=0,NOT(ISNUMBER(E52))),"",E52/B52)</f>
         <v>0.3554594</v>
       </c>
       <c r="G52" s="27">
-        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),E52,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim")),IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),E52,"")</f>
         <v>2488.2158</v>
       </c>
-      <c r="H52" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Custo-hora zero: o fixo cobre as despesas absorvidas","Custo-hora zero, mas o fixo não cobre as despesas absorvidas"),"Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")"),"Preencha horas e valores")))</f>
+      <c r="H52" s="40" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Custo-hora zero: o fixo cobre as despesas absorvidas","Custo-hora zero, mas o fixo não cobre as despesas absorvidas"),"Até "&amp;ROUND(($B$44*(1-Config!$B$7)-$D$39)/$B$11,0)&amp;" horas sem prejuízo (estimadas: "&amp;ROUND($B$29,0)&amp;")"),"Preencha horas e valores"))))</f>
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
-      <c r="I52" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar")))))</f>
+      <c r="I52" s="28" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
@@ -1840,22 +1856,22 @@
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),"")))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),""))))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
       <c r="B53" s="27">
-        <f>$B$45*$B$29</f>
+        <f>IF(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE),$B$45*$B$29,"")</f>
         <v>9540</v>
       </c>
       <c r="C53" s="27">
-        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B53*Config!$B$7)</f>
+        <f>IF(OR((Config!$B$13&lt;&gt;"Sim"),NOT(ISNUMBER(B53))),"",B53*Config!$B$7)</f>
         <v>763.2</v>
       </c>
       <c r="D53" s="27">
@@ -1866,20 +1882,20 @@
         <f>IF(AND(ISNUMBER(C53),ISNUMBER(D53)),B53-C53-D53,"")</f>
         <v>4825.0158</v>
       </c>
-      <c r="F53" s="38">
+      <c r="F53" s="39">
         <f>IF(OR(B53=0,NOT(ISNUMBER(E53))),"",E53/B53)</f>
         <v>0.505766855345912</v>
       </c>
       <c r="G53" s="27">
-        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),E53,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim")),IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),E53,"")</f>
         <v>4825.0158</v>
       </c>
-      <c r="H53" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores")))</f>
+      <c r="H53" s="40" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR("Hora mínima sem prejuízo: R$ "&amp;FIXED($D$40/($B$29*(1-Config!$B$7)),2)&amp;" (você cobra R$ "&amp;FIXED($B$45,2)&amp;")","Preencha horas e valores"))))</f>
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
-      <c r="I53" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar")))))</f>
+      <c r="I53" s="28" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
@@ -1887,22 +1903,22 @@
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),"")))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t>Êxito</t>
         </is>
       </c>
       <c r="B54" s="27">
-        <f>$B$46*$B$14</f>
+        <f>IF(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE)),$B$46*$B$14,"")</f>
         <v>8250</v>
       </c>
       <c r="C54" s="27">
-        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B54*Config!$B$7)</f>
+        <f>IF(OR((Config!$B$13&lt;&gt;"Sim"),NOT(ISNUMBER(B54))),"",B54*Config!$B$7)</f>
         <v>660</v>
       </c>
       <c r="D54" s="27">
@@ -1913,20 +1929,20 @@
         <f>IF(AND(ISNUMBER(C54),ISNUMBER(D54)),B54-C54-D54,"")</f>
         <v>3638.2158</v>
       </c>
-      <c r="F54" s="38">
+      <c r="F54" s="39">
         <f>IF(OR(B54=0,NOT(ISNUMBER(E54))),"",E54/B54)</f>
         <v>0.440995854545455</v>
       </c>
       <c r="G54" s="27">
-        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),-$D$40,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim")),AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),-$D$40,"")</f>
         <v>-3951.7842</v>
       </c>
-      <c r="H54" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF(($B$46*$B$12*(1-Config!$B$7))&lt;=0,"Sem percentual de êxito ou valor em discussão: o êxito não paga o custo","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores")))</f>
+      <c r="H54" s="40" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(($B$46*$B$12*(1-Config!$B$7))&lt;=0,"Sem percentual de êxito ou valor em discussão: o êxito não paga o custo","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND($D$40/($B$46*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)"),"Preencha horas e valores"))))</f>
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
-      <c r="I54" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar")))))</f>
+      <c r="I54" s="28" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar"))))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
@@ -1934,22 +1950,22 @@
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),"")))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),""))))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>Misto</t>
         </is>
       </c>
       <c r="B55" s="27">
-        <f>$B$47+$B$48*$B$14</f>
+        <f>IF(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE)),$B$47+$B$48*$B$14,"")</f>
         <v>9450</v>
       </c>
       <c r="C55" s="27">
-        <f>IF((Config!$B$13&lt;&gt;"Sim"),"",B55*Config!$B$7)</f>
+        <f>IF(OR((Config!$B$13&lt;&gt;"Sim"),NOT(ISNUMBER(B55))),"",B55*Config!$B$7)</f>
         <v>756</v>
       </c>
       <c r="D55" s="27">
@@ -1960,20 +1976,20 @@
         <f>IF(AND(ISNUMBER(C55),ISNUMBER(D55)),B55-C55-D55,"")</f>
         <v>4742.2158</v>
       </c>
-      <c r="F55" s="38">
+      <c r="F55" s="39">
         <f>IF(OR(B55=0,NOT(ISNUMBER(E55))),"",E55/B55)</f>
         <v>0.501821777777778</v>
       </c>
       <c r="G55" s="27">
-        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim"))),$B$47*(1-Config!$B$7)-$D$40,"")</f>
+        <f>IF(AND(ISNUMBER($D$40),NOT((Config!$B$13&lt;&gt;"Sim")),AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),$B$47*(1-Config!$B$7)-$D$40,"")</f>
         <v>188.2158</v>
       </c>
-      <c r="H55" s="39" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora (B11)",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"A entrada já cobre o custo do caso; o êxito é margem",IF(($B$48*$B$12*(1-Config!$B$7))&lt;=0,"A entrada não cobre o custo e não há êxito que complete","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)")),"Preencha horas e valores")))</f>
+      <c r="H55" s="40" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"A entrada já cobre o custo do caso; o êxito é margem",IF(($B$48*$B$12*(1-Config!$B$7))&lt;=0,"A entrada não cobre o custo e não há êxito que complete","Chance mínima de êxito para não ter prejuízo: "&amp;ROUND(($D$40-$B$47*(1-Config!$B$7))/($B$48*$B$12*(1-Config!$B$7))*100,0)&amp;"% (estimada: "&amp;ROUND($B$13*100,0)&amp;"%)")),"Preencha horas e valores"))))</f>
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
-      <c r="I55" s="40" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Falta o custo-hora",IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar")))))</f>
+      <c r="I55" s="28" t="str">
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
@@ -1981,7 +1997,7 @@
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),"Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco.",IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),"")))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),""))))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2016,7 +2032,7 @@
   </mergeCells>
   <conditionalFormatting sqref="I52:I55">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>OR(I52="Alto",I52="Falta o custo-hora",I52="Margens inválidas",I52="Regra de risco inválida (Config)",I52="Sem base para classificar")</formula>
+      <formula>AND(I52&lt;&gt;"",I52&lt;&gt;"Baixo",I52&lt;&gt;"Médio",I52&lt;&gt;"Faltam as horas estimadas")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>I52="Médio"</formula>
@@ -2035,12 +2051,36 @@
       <formula>$A52=$A$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="9">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$E$5,0,0,MAX(1,COUNTA(Config!$E$5:$E$30)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="C33:C38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número de 0 a 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número de 0 a 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número de 0 a 100 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2259,7 +2299,7 @@
           <t>Aceitar risco médio na recomendação?</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -2277,7 +2317,7 @@
           <t>Impostos e margem conferem? (calculado)</t>
         </is>
       </c>
-      <c r="B13" s="40" t="str">
+      <c r="B13" s="28" t="str">
         <f>IF(AND(ISNUMBER(B7),ISNUMBER(B8)),IF(AND(B7&gt;=0,B7&lt;1,B8&gt;=0,B8&lt;1,B7+B8&lt;1),"Sim","Não"),"Não")</f>
         <v>Sim</v>
       </c>
@@ -2294,7 +2334,7 @@
           <t>Regras de risco conferem? (calculado)</t>
         </is>
       </c>
-      <c r="B14" s="40" t="str">
+      <c r="B14" s="28" t="str">
         <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B11)),IF(AND(B9&gt;=0,B9&lt;=1,B10&gt;=0,B10&lt;=1,B11&gt;=0,B11&lt;=1,OR(B12="Sim",B12="Não")),"Sim","Não"),"Não")</f>
         <v>Sim</v>
       </c>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1359,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="27">
-        <f>IF(B19="","",IF(NOT(ISNUMBER(B19)),"horas inválidas",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A19="",B19=""),"",IF(NOT(IF(ISNUMBER(B19),B19&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora")))</f>
         <v>264.2856</v>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="27">
-        <f>IF(B20="","",IF(NOT(ISNUMBER(B20)),"horas inválidas",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A20="",B20=""),"",IF(NOT(IF(ISNUMBER(B20),B20&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora")))</f>
         <v>396.4284</v>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="27">
-        <f>IF(B21="","",IF(NOT(ISNUMBER(B21)),"horas inválidas",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A21="",B21=""),"",IF(NOT(IF(ISNUMBER(B21),B21&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora")))</f>
         <v>792.8568</v>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="27">
-        <f>IF(B22="","",IF(NOT(ISNUMBER(B22)),"horas inválidas",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A22="",B22=""),"",IF(NOT(IF(ISNUMBER(B22),B22&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora")))</f>
         <v>1321.428</v>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="27">
-        <f>IF(B23="","",IF(NOT(ISNUMBER(B23)),"horas inválidas",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A23="",B23=""),"",IF(NOT(IF(ISNUMBER(B23),B23&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora")))</f>
         <v>528.5712</v>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="27">
-        <f>IF(B24="","",IF(NOT(ISNUMBER(B24)),"horas inválidas",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A24="",B24=""),"",IF(NOT(IF(ISNUMBER(B24),B24&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora")))</f>
         <v>198.2142</v>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="A25" s="21" t="n"/>
       <c r="B25" s="30" t="n"/>
       <c r="C25" s="27">
-        <f>IF(B25="","",IF(NOT(ISNUMBER(B25)),"horas inválidas",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A25="",B25=""),"",IF(NOT(IF(ISNUMBER(B25),B25&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       <c r="A26" s="21" t="n"/>
       <c r="B26" s="30" t="n"/>
       <c r="C26" s="27">
-        <f>IF(B26="","",IF(NOT(ISNUMBER(B26)),"horas inválidas",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A26="",B26=""),"",IF(NOT(IF(ISNUMBER(B26),B26&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="A27" s="21" t="n"/>
       <c r="B27" s="30" t="n"/>
       <c r="C27" s="27">
-        <f>IF(B27="","",IF(NOT(ISNUMBER(B27)),"horas inválidas",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A27="",B27=""),"",IF(NOT(IF(ISNUMBER(B27),B27&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       <c r="A28" s="21" t="n"/>
       <c r="B28" s="30" t="n"/>
       <c r="C28" s="27">
-        <f>IF(B28="","",IF(NOT(ISNUMBER(B28)),"horas inválidas",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A28="",B28=""),"",IF(NOT(IF(ISNUMBER(B28),B28&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B29" s="32">
-        <f>SUM(B19:B28)</f>
+        <f>IF(SUMPRODUCT(((A19:A28&lt;&gt;"")+(B19:B28&lt;&gt;"")&gt;0)*((ISNUMBER(B19:B28)=FALSE)+ISNUMBER(B19:B28)*(B19:B28&lt;0)&gt;0))=0,SUM(B19:B28),"horas faltando ou inválidas")</f>
         <v>53</v>
       </c>
       <c r="C29" s="33">
-        <f>IF(NOT(ISNUMBER($B$11)),"falta o custo-hora",IF(COUNT(B19:B28)&lt;COUNTA(B19:B28),"horas com texto",SUM(C19:C28)))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"falta o custo-hora",IF(SUMPRODUCT(((A19:A28&lt;&gt;"")+(B19:B28&lt;&gt;"")&gt;0)*((ISNUMBER(B19:B28)=FALSE)+ISNUMBER(B19:B28)*(B19:B28&lt;0)&gt;0))&gt;0,"horas faltando ou inválidas",SUM(C19:C28)))</f>
         <v>3501.7842</v>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="D33" s="27">
-        <f>IF(B33="","",IF(NOT(ISNUMBER(B33)),"valor inválido",IF(C33="Sim",0,B33)))</f>
+        <f>IF(AND(A33="",B33="",C33=""),"",IF(NOT(IF(ISNUMBER(B33),B33&gt;=0,FALSE)),"falta o valor",IF(AND(C33&lt;&gt;"Sim",C33&lt;&gt;"Não"),"falta: reembolsa?",IF(C33="Sim",0,B33))))</f>
         <v>0</v>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="D34" s="27">
-        <f>IF(B34="","",IF(NOT(ISNUMBER(B34)),"valor inválido",IF(C34="Sim",0,B34)))</f>
+        <f>IF(AND(A34="",B34="",C34=""),"",IF(NOT(IF(ISNUMBER(B34),B34&gt;=0,FALSE)),"falta o valor",IF(AND(C34&lt;&gt;"Sim",C34&lt;&gt;"Não"),"falta: reembolsa?",IF(C34="Sim",0,B34))))</f>
         <v>300</v>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D35" s="27">
-        <f>IF(B35="","",IF(NOT(ISNUMBER(B35)),"valor inválido",IF(C35="Sim",0,B35)))</f>
+        <f>IF(AND(A35="",B35="",C35=""),"",IF(NOT(IF(ISNUMBER(B35),B35&gt;=0,FALSE)),"falta o valor",IF(AND(C35&lt;&gt;"Sim",C35&lt;&gt;"Não"),"falta: reembolsa?",IF(C35="Sim",0,B35))))</f>
         <v>150</v>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D36" s="27">
-        <f>IF(B36="","",IF(NOT(ISNUMBER(B36)),"valor inválido",IF(C36="Sim",0,B36)))</f>
+        <f>IF(AND(A36="",B36="",C36=""),"",IF(NOT(IF(ISNUMBER(B36),B36&gt;=0,FALSE)),"falta o valor",IF(AND(C36&lt;&gt;"Sim",C36&lt;&gt;"Não"),"falta: reembolsa?",IF(C36="Sim",0,B36))))</f>
         <v>0</v>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       <c r="B37" s="22" t="n"/>
       <c r="C37" s="34" t="n"/>
       <c r="D37" s="27">
-        <f>IF(B37="","",IF(NOT(ISNUMBER(B37)),"valor inválido",IF(C37="Sim",0,B37)))</f>
+        <f>IF(AND(A37="",B37="",C37=""),"",IF(NOT(IF(ISNUMBER(B37),B37&gt;=0,FALSE)),"falta o valor",IF(AND(C37&lt;&gt;"Sim",C37&lt;&gt;"Não"),"falta: reembolsa?",IF(C37="Sim",0,B37))))</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       <c r="B38" s="22" t="n"/>
       <c r="C38" s="34" t="n"/>
       <c r="D38" s="27">
-        <f>IF(B38="","",IF(NOT(ISNUMBER(B38)),"valor inválido",IF(C38="Sim",0,B38)))</f>
+        <f>IF(AND(A38="",B38="",C38=""),"",IF(NOT(IF(ISNUMBER(B38),B38&gt;=0,FALSE)),"falta o valor",IF(AND(C38&lt;&gt;"Sim",C38&lt;&gt;"Não"),"falta: reembolsa?",IF(C38="Sim",0,B38))))</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
         <v>1250</v>
       </c>
       <c r="D39" s="33">
-        <f>IF(COUNT(B33:B38)&lt;COUNTA(B33:B38),"despesa com texto",SUM(D33:D38))</f>
+        <f>IF(SUMPRODUCT(((A33:A38&lt;&gt;"")+(B33:B38&lt;&gt;"")+(C33:C38&lt;&gt;"")&gt;0)*(ISNUMBER(D33:D38)=FALSE))&gt;0,"despesa incompleta",SUM(D33:D38))</f>
         <v>450</v>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="D40" s="33">
-        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($C$29)),"Horas com texto (bloco 2)",IF(NOT(ISNUMBER($D$39)),"Despesa com texto (bloco 3)",$C$29+$D$39)))</f>
+        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($C$29)),"Horas faltando ou inválidas (bloco 2)",IF(NOT(ISNUMBER($D$39)),"Despesa incompleta (bloco 3)",$C$29+$D$39)))</f>
         <v>3951.7842</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
@@ -1856,7 +1856,7 @@
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),""))))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="B53" s="27">
-        <f>IF(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE),$B$45*$B$29,"")</f>
+        <f>IF(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE),IF(SUMPRODUCT((($A$19:$A$28&lt;&gt;"")+($B$19:$B$28&lt;&gt;"")&gt;0)*((ISNUMBER($B$19:$B$28)=FALSE)+ISNUMBER($B$19:$B$28)*($B$19:$B$28&lt;0)&gt;0))=0,$B$45*$B$29,""),"")</f>
         <v>9540</v>
       </c>
       <c r="C53" s="27">
@@ -1895,7 +1895,7 @@
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
@@ -1903,7 +1903,7 @@
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar"))))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
@@ -1950,7 +1950,7 @@
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),""))))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas com texto","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
@@ -1997,7 +1997,7 @@
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: há texto onde deveria haver horas ou valor de despesa.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),""))))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2051,12 +2051,18 @@
       <formula>$A52=$A$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="11">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$E$5,0,0,MAX(1,COUNTA(Config!$E$5:$E$30)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="C33:C38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B19:B28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B33:B38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/06-simulador-de-honorarios.xlsx
@@ -1158,7 +1158,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="str">
-        <f>IF(NOT(ISNUMBER($B$11)),"Preencha o custo-hora primeiro",IF(NOT(ISNUMBER($D$40)),"Corrija horas ou despesas",IF($B$16&lt;&gt;"Sim","Complete os dados do caso",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(Config!$B$14&lt;&gt;"Sim","Corrija as regras de risco em Config",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))))))))</f>
+        <f>IF(NOT(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE)),"Preencha o custo-hora primeiro",IF(NOT(ISNUMBER($D$40)),"Corrija horas ou despesas",IF($B$16&lt;&gt;"Sim","Complete os dados do caso",IF((Config!$B$13&lt;&gt;"Sim"),"Corrija as margens em Config",IF($B$29&lt;=0,"Estime as horas primeiro",IF(Config!$B$14&lt;&gt;"Sim","Corrija as regras de risco em Config",IF(MAX($J$52:$J$55)&lt;=-1E+9,"Nenhuma com risco aceitável",INDEX($A$52:$A$55,MATCH(MAX($J$52:$J$55),$J$52:$J$55,0)))))))))</f>
         <v>Hora</v>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="B15" s="27">
-        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),""))))</f>
+        <f>IF(NOT(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($D$40)),$D$40,IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas (Config)",IFERROR(IF($B$29=0,B11/(1-Config!$B$7-Config!$B$8),($D$40/$B$29)/(1-Config!$B$7-Config!$B$8)),""))))</f>
         <v>120.261235544735</v>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1359,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="27">
-        <f>IF(AND(A19="",B19=""),"",IF(NOT(IF(ISNUMBER(B19),B19&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B19*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A19="",B19=""),"",IF(NOT(IF(ISNUMBER(B19),B19&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B19*$B$11,"falta o custo-hora")))</f>
         <v>264.2856</v>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="27">
-        <f>IF(AND(A20="",B20=""),"",IF(NOT(IF(ISNUMBER(B20),B20&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B20*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A20="",B20=""),"",IF(NOT(IF(ISNUMBER(B20),B20&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B20*$B$11,"falta o custo-hora")))</f>
         <v>396.4284</v>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="27">
-        <f>IF(AND(A21="",B21=""),"",IF(NOT(IF(ISNUMBER(B21),B21&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B21*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A21="",B21=""),"",IF(NOT(IF(ISNUMBER(B21),B21&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B21*$B$11,"falta o custo-hora")))</f>
         <v>792.8568</v>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="27">
-        <f>IF(AND(A22="",B22=""),"",IF(NOT(IF(ISNUMBER(B22),B22&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B22*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A22="",B22=""),"",IF(NOT(IF(ISNUMBER(B22),B22&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B22*$B$11,"falta o custo-hora")))</f>
         <v>1321.428</v>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="27">
-        <f>IF(AND(A23="",B23=""),"",IF(NOT(IF(ISNUMBER(B23),B23&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B23*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A23="",B23=""),"",IF(NOT(IF(ISNUMBER(B23),B23&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B23*$B$11,"falta o custo-hora")))</f>
         <v>528.5712</v>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="27">
-        <f>IF(AND(A24="",B24=""),"",IF(NOT(IF(ISNUMBER(B24),B24&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B24*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A24="",B24=""),"",IF(NOT(IF(ISNUMBER(B24),B24&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B24*$B$11,"falta o custo-hora")))</f>
         <v>198.2142</v>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       <c r="A25" s="21" t="n"/>
       <c r="B25" s="30" t="n"/>
       <c r="C25" s="27">
-        <f>IF(AND(A25="",B25=""),"",IF(NOT(IF(ISNUMBER(B25),B25&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B25*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A25="",B25=""),"",IF(NOT(IF(ISNUMBER(B25),B25&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B25*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       <c r="A26" s="21" t="n"/>
       <c r="B26" s="30" t="n"/>
       <c r="C26" s="27">
-        <f>IF(AND(A26="",B26=""),"",IF(NOT(IF(ISNUMBER(B26),B26&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B26*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A26="",B26=""),"",IF(NOT(IF(ISNUMBER(B26),B26&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B26*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       <c r="A27" s="21" t="n"/>
       <c r="B27" s="30" t="n"/>
       <c r="C27" s="27">
-        <f>IF(AND(A27="",B27=""),"",IF(NOT(IF(ISNUMBER(B27),B27&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B27*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A27="",B27=""),"",IF(NOT(IF(ISNUMBER(B27),B27&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B27*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       <c r="A28" s="21" t="n"/>
       <c r="B28" s="30" t="n"/>
       <c r="C28" s="27">
-        <f>IF(AND(A28="",B28=""),"",IF(NOT(IF(ISNUMBER(B28),B28&gt;=0,FALSE)),"faltam as horas",IF(ISNUMBER($B$11),B28*$B$11,"falta o custo-hora")))</f>
+        <f>IF(AND(A28="",B28=""),"",IF(NOT(IF(ISNUMBER(B28),B28&gt;=0,FALSE)),"faltam as horas",IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),B28*$B$11,"falta o custo-hora")))</f>
         <v/>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>53</v>
       </c>
       <c r="C29" s="33">
-        <f>IF(NOT(ISNUMBER($B$11)),"falta o custo-hora",IF(SUMPRODUCT(((A19:A28&lt;&gt;"")+(B19:B28&lt;&gt;"")&gt;0)*((ISNUMBER(B19:B28)=FALSE)+ISNUMBER(B19:B28)*(B19:B28&lt;0)&gt;0))&gt;0,"horas faltando ou inválidas",SUM(C19:C28)))</f>
+        <f>IF(NOT(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE)),"falta o custo-hora",IF(SUMPRODUCT(((A19:A28&lt;&gt;"")+(B19:B28&lt;&gt;"")&gt;0)*((ISNUMBER(B19:B28)=FALSE)+ISNUMBER(B19:B28)*(B19:B28&lt;0)&gt;0))&gt;0,"horas faltando ou inválidas",SUM(C19:C28)))</f>
         <v>3501.7842</v>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="B39" s="27">
-        <f>SUM(B33:B38)</f>
+        <f>IF(SUMPRODUCT(((A33:A38&lt;&gt;"")+(B33:B38&lt;&gt;"")+(C33:C38&lt;&gt;"")&gt;0)*((ISNUMBER(B33:B38)=FALSE)+ISNUMBER(B33:B38)*(B33:B38&lt;0)&gt;0))&gt;0,"despesa incompleta",SUM(B33:B38))</f>
         <v>1250</v>
       </c>
       <c r="D39" s="33">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="D40" s="33">
-        <f>IF(NOT(ISNUMBER($B$11)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($C$29)),"Horas faltando ou inválidas (bloco 2)",IF(NOT(ISNUMBER($D$39)),"Despesa incompleta (bloco 3)",$C$29+$D$39)))</f>
+        <f>IF(NOT(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE)),"Falta o custo-hora (B11)",IF(NOT(ISNUMBER($C$29)),"Horas faltando ou inválidas (bloco 2)",IF(NOT(ISNUMBER($D$39)),"Despesa incompleta (bloco 3)",$C$29+$D$39)))</f>
         <v>3951.7842</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         <v>Até 91 horas sem prejuízo (estimadas: 53)</v>
       </c>
       <c r="I52" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Falta o valor do fixo",IFERROR(IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29*(1+Config!$B$11),"Baixo",IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=$B$11*$B$29,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J52" s="41">
@@ -1856,7 +1856,7 @@
         <v>2488.2158</v>
       </c>
       <c r="K52" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0,Config!$B$11&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$44),AND($B$44&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$11=0,IF(($B$44*(1-Config!$B$7)-$D$39)&gt;=0,"Sem custo de hora: só as despesas absorvidas contam, e o fixo as cobre","O fixo não cobre nem as despesas absorvidas"),"Folga de horas: "&amp;ROUND((($B$44*(1-Config!$B$7)-$D$39)/$B$11/$B$29-1)*100,0)&amp;"% (mínimo para risco baixo: "&amp;ROUND(Config!$B$11*100,0)&amp;"%)"),""))))))</f>
         <v>Folga de horas: 71% (mínimo para risco baixo: 20%)</v>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
         <v>Hora mínima sem prejuízo: R$ 81,05 (você cobra R$ 180,00)</v>
       </c>
       <c r="I53" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(TRUE),"Regra de risco inválida (Config)",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Falta a hora cobrada",IFERROR(IF($B$45&gt;=$B$15,"Baixo",IF($B$45*$B$29*(1-Config!$B$7)&gt;=$D$40,"Médio","Alto")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J53" s="41">
@@ -1903,7 +1903,7 @@
         <v>4825.0158</v>
       </c>
       <c r="K53" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(TRUE),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(IF(ISNUMBER($B$45),AND($B$45&gt;=0),FALSE)),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$45&gt;=$B$15,"A hora cobrada cobre custo, impostos e margem desejada","A hora cobrada fica abaixo da hora mínima com margem (R$ "&amp;FIXED($B$15,2)&amp;")"),""))))))</f>
         <v>A hora cobrada cobre custo, impostos e margem desejada</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>Chance mínima de êxito para não ter prejuízo: 29% (estimada: 55%)</v>
       </c>
       <c r="I54" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta % de êxito, valor ou chance",IFERROR(IF(OR($B$13&lt;Config!$B$9,($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40),"Alto","Médio"),"Sem base para classificar"))))))</f>
         <v>Alto</v>
       </c>
       <c r="J54" s="41">
@@ -1950,7 +1950,7 @@
         <v>-1000000000</v>
       </c>
       <c r="K54" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(AND(IF(ISNUMBER(Config!$B$9),AND(Config!$B$9&gt;=0,Config!$B$9&lt;=1),FALSE),IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE))),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$46),AND($B$46&gt;=0,$B$46&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF($B$13&lt;Config!$B$9,"Chance estimada abaixo do mínimo aceitável para êxito puro ("&amp;ROUND(Config!$B$9*100,0)&amp;"%)",IF(($B$13-Config!$B$10)*($B$46*$B$12*(1-Config!$B$7))&lt;$D$40,"Chance estimada perto demais do ponto de equilíbrio (ou sem êxito que pague o custo)","Só recebe no fim; o caixa precisa aguentar até lá")),""))))))</f>
         <v>Chance estimada abaixo do mínimo aceitável para êxito puro (60%)</v>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
         <v>A entrada já cobre o custo do caso; o êxito é margem</v>
       </c>
       <c r="I55" s="28" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar"))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Horas ou despesas incompletas","Falta o custo-hora"),IF((Config!$B$13&lt;&gt;"Sim"),"Margens inválidas",IF($B$29&lt;=0,"Faltam as horas estimadas",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"Regra de risco inválida (Config)",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Falta entrada, %, valor ou chance",IFERROR(IF(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,$B$13&lt;Config!$B$10,($B$13-Config!$B$10)*($B$48*$B$12*(1-Config!$B$7))&lt;($D$40-$B$47*(1-Config!$B$7))),"Alto",IF(($D$40-$B$47*(1-Config!$B$7))&gt;0,"Médio","Baixo")),"Sem base para classificar"))))))</f>
         <v>Baixo</v>
       </c>
       <c r="J55" s="41">
@@ -1997,7 +1997,7 @@
         <v>4742.2158</v>
       </c>
       <c r="K55" s="42" t="str">
-        <f>IF(NOT(ISNUMBER($D$40)),IF(ISNUMBER($B$11),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),""))))))</f>
+        <f>IF(NOT(ISNUMBER($D$40)),IF(IF(ISNUMBER($B$11),$B$11&gt;=0,FALSE),"Corrija o bloco 2 ou 3: etapa sem horas (ou negativa), despesa sem valor ou sem a resposta de reembolso.","Preencha o custo-hora do escritório (B11): sem ele não há custo do caso, margem nem risco."),IF((Config!$B$13&lt;&gt;"Sim"),"Impostos e margem em Config fora do permitido (cada um de 0 % a 99 %, soma abaixo de 100 %). Corrija a Config.",IF($B$29&lt;=0,"Preencha as horas estimadas no bloco 2: sem elas não há custo do caso por hora, nem margem, nem ponto de equilíbrio.",IF(NOT(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0,Config!$B$10&lt;=1),FALSE)),"A regra de risco desta modalidade em Config está vazia ou fora de 0 % a 100 %. Corrija a Config.",IF(NOT(AND(IF(ISNUMBER($B$47),AND($B$47&gt;=0),FALSE),IF(ISNUMBER($B$48),AND($B$48&gt;=0,$B$48&lt;=1),FALSE),IF(ISNUMBER($B$12),AND($B$12&gt;=0),FALSE),IF(ISNUMBER($B$13),AND($B$13&gt;=0,$B$13&lt;=1),FALSE))),"Preencha no bloco 1 ou 4 o dado que falta: "&amp;$B$16&amp;".",IFERROR(IF(($D$40-$B$47*(1-Config!$B$7))&lt;=0,"Entrada cobre o custo: mesmo perdendo, não há prejuízo","Entrada não cobre todo o custo; parte depende do êxito"),""))))))</f>
         <v>Entrada cobre o custo: mesmo perdendo, não há prejuízo</v>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       <formula>$A52=$A$5</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$E$5,0,0,MAX(1,COUNTA(Config!$E$5:$E$30)),1)</formula1>
     </dataValidation>
@@ -2088,6 +2088,9 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custo-hora" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
